--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>120672030</v>
       </c>
       <c r="B4" t="n">
-        <v>98056</v>
+        <v>98066</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1046,6 +1046,250 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>121454148</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98066</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219799</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kärrknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis palustris</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Öja Strands 1:31, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>696608</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6325056</v>
+      </c>
+      <c r="S5" t="n">
+        <v>23</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>I fuktängsmiljö med temporära småvatten.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>121454151</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98083</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219811</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brudsporre</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Gymnadenia conopsea</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Öja Strands 1:31, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>696608</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6325056</v>
+      </c>
+      <c r="S6" t="n">
+        <v>23</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Öja</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-11-01</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>I fuktängsmiljö med temporära småvatten.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Bolander</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>120672030</v>
       </c>
       <c r="B4" t="n">
-        <v>98066</v>
+        <v>98079</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>121454148</v>
       </c>
       <c r="B5" t="n">
-        <v>98066</v>
+        <v>98079</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>121454151</v>
       </c>
       <c r="B6" t="n">
-        <v>98083</v>
+        <v>98096</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>120672030</v>
       </c>
       <c r="B4" t="n">
-        <v>98079</v>
+        <v>98080</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121454148</v>
+        <v>121454151</v>
       </c>
       <c r="B5" t="n">
-        <v>98079</v>
+        <v>98097</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,21 +1064,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121454151</v>
+        <v>121454148</v>
       </c>
       <c r="B6" t="n">
-        <v>98096</v>
+        <v>98080</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -929,7 +929,7 @@
         <v>120672030</v>
       </c>
       <c r="B4" t="n">
-        <v>98080</v>
+        <v>98083</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>121454151</v>
       </c>
       <c r="B5" t="n">
-        <v>98097</v>
+        <v>98100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>121454148</v>
       </c>
       <c r="B6" t="n">
-        <v>98080</v>
+        <v>98083</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121454151</v>
+        <v>121454148</v>
       </c>
       <c r="B5" t="n">
-        <v>98100</v>
+        <v>98083</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,21 +1064,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121454148</v>
+        <v>121454151</v>
       </c>
       <c r="B6" t="n">
-        <v>98083</v>
+        <v>98100</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121454148</v>
+        <v>121454151</v>
       </c>
       <c r="B5" t="n">
-        <v>98083</v>
+        <v>98106</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,21 +1064,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121454151</v>
+        <v>121454148</v>
       </c>
       <c r="B6" t="n">
-        <v>98100</v>
+        <v>98089</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121454151</v>
+        <v>121454148</v>
       </c>
       <c r="B5" t="n">
-        <v>98106</v>
+        <v>98090</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,21 +1064,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121454148</v>
+        <v>121454151</v>
       </c>
       <c r="B6" t="n">
-        <v>98089</v>
+        <v>98107</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121454148</v>
+        <v>121454151</v>
       </c>
       <c r="B5" t="n">
-        <v>98090</v>
+        <v>98107</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,21 +1064,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121454151</v>
+        <v>121454148</v>
       </c>
       <c r="B6" t="n">
-        <v>98107</v>
+        <v>98090</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -1048,10 +1048,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121454151</v>
+        <v>121454148</v>
       </c>
       <c r="B5" t="n">
-        <v>98107</v>
+        <v>98090</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1064,21 +1064,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121454148</v>
+        <v>121454151</v>
       </c>
       <c r="B6" t="n">
-        <v>98090</v>
+        <v>98107</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1186,21 +1186,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>104790</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107224</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696635.3018366086</v>
+        <v>696635</v>
       </c>
       <c r="R2" t="n">
-        <v>6325105.415894177</v>
+        <v>6325105</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>1999-07-09</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1999-07-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,12 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>107967</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>110439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>696635.3018366086</v>
+        <v>696635</v>
       </c>
       <c r="R3" t="n">
-        <v>6325105.415894177</v>
+        <v>6325105</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -878,19 +858,9 @@
           <t>1999-07-09</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1999-07-09</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>107224</v>
+        <v>107233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>110439</v>
+        <v>110448</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>107233</v>
+        <v>107245</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>110448</v>
+        <v>110461</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>107245</v>
+        <v>107254</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>110461</v>
+        <v>110470</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>107254</v>
+        <v>107259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>110470</v>
+        <v>110475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>107259</v>
+        <v>107287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>110475</v>
+        <v>110503</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>107287</v>
+        <v>107293</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>110503</v>
+        <v>110509</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>107293</v>
+        <v>107300</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>110509</v>
+        <v>110516</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>107300</v>
+        <v>107304</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>110516</v>
+        <v>110520</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>107304</v>
+        <v>107312</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>110520</v>
+        <v>110528</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>107315</v>
+        <v>107320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>110531</v>
+        <v>110536</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>104704679</v>
       </c>
       <c r="B2" t="n">
-        <v>107320</v>
+        <v>107328</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>104704680</v>
       </c>
       <c r="B3" t="n">
-        <v>110536</v>
+        <v>110544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -675,35 +675,44 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104704679</v>
+        <v>104704680</v>
       </c>
       <c r="B2" t="n">
-        <v>107328</v>
+        <v>111144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1855</v>
+        <v>1644</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkerkulla</t>
+          <t>Sommarklynne</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Anthemis arvensis</t>
+          <t>Valerianella dentata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Pollich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Mjölhatteträsk just NO, Gisle 1:38 130 m SV, Gtl</t>
@@ -781,44 +790,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104704680</v>
+        <v>104704679</v>
       </c>
       <c r="B3" t="n">
-        <v>110544</v>
+        <v>107868</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1644</v>
+        <v>1855</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sommarklynne</t>
+          <t>Åkerkulla</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Valerianella dentata</t>
+          <t>Anthemis arvensis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Pollich</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Mjölhatteträsk just NO, Gisle 1:38 130 m SV, Gtl</t>
@@ -899,12 +899,7 @@
         <v>120672030</v>
       </c>
       <c r="B4" t="n">
-        <v>98083</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,15 +1013,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121454151</v>
+        <v>121454148</v>
       </c>
       <c r="B5" t="n">
-        <v>98115</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99103</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1034,21 +1024,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219811</v>
+        <v>219799</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Kärrknipprot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Epipactis palustris</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1140,15 +1130,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121454148</v>
+        <v>121454151</v>
       </c>
       <c r="B6" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1156,21 +1141,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219799</v>
+        <v>219811</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kärrknipprot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Epipactis palustris</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>

--- a/artfynd/A 54523-2023 artfynd.xlsx
+++ b/artfynd/A 54523-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -787,6 +792,11 @@
           <t>Projekt Gotlands Flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104704680</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
       <c r="AY3" t="inlineStr">
         <is>
           <t>Projekt Gotlands Flora</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104704679</t>
         </is>
       </c>
     </row>
@@ -1010,6 +1025,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120672030</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1127,6 +1147,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121454148</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1244,8 +1269,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121454151</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>